--- a/artfynd/A 59832-2023 artfynd.xlsx
+++ b/artfynd/A 59832-2023 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130187836</v>
+        <v>130187862</v>
       </c>
       <c r="B7" t="n">
-        <v>79095</v>
+        <v>82939</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>780029</v>
+        <v>780081</v>
       </c>
       <c r="R7" t="n">
-        <v>7274587</v>
+        <v>7274609</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1347,32 +1347,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130187852</v>
+        <v>130187836</v>
       </c>
       <c r="B8" t="n">
-        <v>5177</v>
+        <v>79095</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>780080</v>
+        <v>780029</v>
       </c>
       <c r="R8" t="n">
-        <v>7274590</v>
+        <v>7274587</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1571,32 +1571,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130187862</v>
+        <v>130187852</v>
       </c>
       <c r="B10" t="n">
-        <v>82939</v>
+        <v>5177</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>780081</v>
+        <v>780080</v>
       </c>
       <c r="R10" t="n">
-        <v>7274609</v>
+        <v>7274590</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130187805</v>
+        <v>130187844</v>
       </c>
       <c r="B12" t="n">
-        <v>57738</v>
+        <v>80200</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,21 +1806,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>779884</v>
+        <v>780089</v>
       </c>
       <c r="R12" t="n">
-        <v>7274509</v>
+        <v>7274562</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1907,32 +1907,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130187844</v>
+        <v>130187809</v>
       </c>
       <c r="B13" t="n">
-        <v>80200</v>
+        <v>5197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>780089</v>
+        <v>779880</v>
       </c>
       <c r="R13" t="n">
-        <v>7274562</v>
+        <v>7274528</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2019,27 +2019,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130187809</v>
+        <v>130187805</v>
       </c>
       <c r="B14" t="n">
-        <v>5197</v>
+        <v>57738</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>779880</v>
+        <v>779884</v>
       </c>
       <c r="R14" t="n">
-        <v>7274528</v>
+        <v>7274509</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2467,32 +2467,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130187824</v>
+        <v>130187822</v>
       </c>
       <c r="B18" t="n">
-        <v>80104</v>
+        <v>79095</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>779977</v>
+        <v>779971</v>
       </c>
       <c r="R18" t="n">
-        <v>7274568</v>
+        <v>7274563</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2579,32 +2579,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130187822</v>
+        <v>130187824</v>
       </c>
       <c r="B19" t="n">
-        <v>79095</v>
+        <v>80104</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>779971</v>
+        <v>779977</v>
       </c>
       <c r="R19" t="n">
-        <v>7274563</v>
+        <v>7274568</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 59832-2023 artfynd.xlsx
+++ b/artfynd/A 59832-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130187874</v>
       </c>
       <c r="B2" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130187876</v>
+        <v>130187821</v>
       </c>
       <c r="B3" t="n">
-        <v>80104</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>780063</v>
+        <v>779968</v>
       </c>
       <c r="R3" t="n">
-        <v>7274578</v>
+        <v>7274543</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130187821</v>
+        <v>130187851</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>779968</v>
+        <v>780086</v>
       </c>
       <c r="R4" t="n">
-        <v>7274543</v>
+        <v>7274586</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1011,32 +1011,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130187851</v>
+        <v>130187876</v>
       </c>
       <c r="B5" t="n">
-        <v>79095</v>
+        <v>80189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>780086</v>
+        <v>780063</v>
       </c>
       <c r="R5" t="n">
-        <v>7274586</v>
+        <v>7274578</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130187862</v>
+        <v>130187836</v>
       </c>
       <c r="B7" t="n">
-        <v>82939</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>780081</v>
+        <v>780029</v>
       </c>
       <c r="R7" t="n">
-        <v>7274609</v>
+        <v>7274587</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1347,32 +1347,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130187836</v>
+        <v>130187852</v>
       </c>
       <c r="B8" t="n">
-        <v>79095</v>
+        <v>5177</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>780029</v>
+        <v>780080</v>
       </c>
       <c r="R8" t="n">
-        <v>7274587</v>
+        <v>7274590</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,7 +1462,7 @@
         <v>130187798</v>
       </c>
       <c r="B9" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,32 +1571,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130187852</v>
+        <v>130187862</v>
       </c>
       <c r="B10" t="n">
-        <v>5177</v>
+        <v>83024</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>780080</v>
+        <v>780081</v>
       </c>
       <c r="R10" t="n">
-        <v>7274590</v>
+        <v>7274609</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1686,7 +1686,7 @@
         <v>130187825</v>
       </c>
       <c r="B11" t="n">
-        <v>80229</v>
+        <v>80314</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130187844</v>
+        <v>130187805</v>
       </c>
       <c r="B12" t="n">
-        <v>80200</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,21 +1806,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>780089</v>
+        <v>779884</v>
       </c>
       <c r="R12" t="n">
-        <v>7274562</v>
+        <v>7274509</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1907,32 +1907,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130187809</v>
+        <v>130187844</v>
       </c>
       <c r="B13" t="n">
-        <v>5197</v>
+        <v>80285</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>779880</v>
+        <v>780089</v>
       </c>
       <c r="R13" t="n">
-        <v>7274528</v>
+        <v>7274562</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2019,27 +2019,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130187805</v>
+        <v>130187809</v>
       </c>
       <c r="B14" t="n">
-        <v>57738</v>
+        <v>5197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>779884</v>
+        <v>779880</v>
       </c>
       <c r="R14" t="n">
-        <v>7274509</v>
+        <v>7274528</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2246,7 +2246,7 @@
         <v>130187819</v>
       </c>
       <c r="B16" t="n">
-        <v>82939</v>
+        <v>83024</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>130187865</v>
       </c>
       <c r="B17" t="n">
-        <v>80229</v>
+        <v>80314</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2467,32 +2467,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130187822</v>
+        <v>130187824</v>
       </c>
       <c r="B18" t="n">
-        <v>79095</v>
+        <v>80189</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>779971</v>
+        <v>779977</v>
       </c>
       <c r="R18" t="n">
-        <v>7274563</v>
+        <v>7274568</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2579,32 +2579,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130187824</v>
+        <v>130187822</v>
       </c>
       <c r="B19" t="n">
-        <v>80104</v>
+        <v>79180</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>779977</v>
+        <v>779971</v>
       </c>
       <c r="R19" t="n">
-        <v>7274568</v>
+        <v>7274563</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2694,7 +2694,7 @@
         <v>130187872</v>
       </c>
       <c r="B20" t="n">
-        <v>80229</v>
+        <v>80314</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>130187832</v>
       </c>
       <c r="B21" t="n">
-        <v>82939</v>
+        <v>83024</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>130187846</v>
       </c>
       <c r="B22" t="n">
-        <v>80229</v>
+        <v>80314</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>130187800</v>
       </c>
       <c r="B23" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>130187799</v>
       </c>
       <c r="B24" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>130187866</v>
       </c>
       <c r="B25" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>130187795</v>
       </c>
       <c r="B27" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>130187841</v>
       </c>
       <c r="B28" t="n">
-        <v>82939</v>
+        <v>83024</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>130187826</v>
       </c>
       <c r="B29" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>130187808</v>
       </c>
       <c r="B30" t="n">
-        <v>57845</v>
+        <v>57930</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 59832-2023 artfynd.xlsx
+++ b/artfynd/A 59832-2023 artfynd.xlsx
@@ -1683,32 +1683,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130187825</v>
+        <v>130187844</v>
       </c>
       <c r="B11" t="n">
-        <v>80314</v>
+        <v>80285</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>779986</v>
+        <v>780089</v>
       </c>
       <c r="R11" t="n">
-        <v>7274565</v>
+        <v>7274562</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1907,32 +1907,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130187844</v>
+        <v>130187809</v>
       </c>
       <c r="B13" t="n">
-        <v>80285</v>
+        <v>5197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>780089</v>
+        <v>779880</v>
       </c>
       <c r="R13" t="n">
-        <v>7274562</v>
+        <v>7274528</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130187809</v>
+        <v>130187825</v>
       </c>
       <c r="B14" t="n">
-        <v>5197</v>
+        <v>80314</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,21 +2030,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>779880</v>
+        <v>779986</v>
       </c>
       <c r="R14" t="n">
-        <v>7274528</v>
+        <v>7274565</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2131,32 +2131,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130187819</v>
+        <v>130187814</v>
       </c>
       <c r="B15" t="n">
-        <v>83024</v>
+        <v>5177</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>779988</v>
+        <v>779905</v>
       </c>
       <c r="R15" t="n">
-        <v>7274540</v>
+        <v>7274531</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2243,32 +2243,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130187814</v>
+        <v>130187819</v>
       </c>
       <c r="B16" t="n">
-        <v>5177</v>
+        <v>83024</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>779905</v>
+        <v>779988</v>
       </c>
       <c r="R16" t="n">
-        <v>7274531</v>
+        <v>7274540</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">

--- a/artfynd/A 59832-2023 artfynd.xlsx
+++ b/artfynd/A 59832-2023 artfynd.xlsx
@@ -2467,32 +2467,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130187822</v>
+        <v>130187824</v>
       </c>
       <c r="B18" t="n">
-        <v>79180</v>
+        <v>80189</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>779971</v>
+        <v>779977</v>
       </c>
       <c r="R18" t="n">
-        <v>7274563</v>
+        <v>7274568</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2579,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130187824</v>
+        <v>130187872</v>
       </c>
       <c r="B19" t="n">
-        <v>80189</v>
+        <v>80314</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2590,21 +2590,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>779977</v>
+        <v>780058</v>
       </c>
       <c r="R19" t="n">
-        <v>7274568</v>
+        <v>7274593</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2691,32 +2691,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130187872</v>
+        <v>130187822</v>
       </c>
       <c r="B20" t="n">
-        <v>80314</v>
+        <v>79180</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>780058</v>
+        <v>779971</v>
       </c>
       <c r="R20" t="n">
-        <v>7274593</v>
+        <v>7274563</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 59832-2023 artfynd.xlsx
+++ b/artfynd/A 59832-2023 artfynd.xlsx
@@ -1235,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130187836</v>
+        <v>130187798</v>
       </c>
       <c r="B7" t="n">
         <v>79180</v>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>780029</v>
+        <v>779985</v>
       </c>
       <c r="R7" t="n">
-        <v>7274587</v>
+        <v>7274468</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1347,32 +1347,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130187852</v>
+        <v>130187836</v>
       </c>
       <c r="B8" t="n">
-        <v>5177</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>780080</v>
+        <v>780029</v>
       </c>
       <c r="R8" t="n">
-        <v>7274590</v>
+        <v>7274587</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,32 +1459,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130187862</v>
+        <v>130187852</v>
       </c>
       <c r="B9" t="n">
-        <v>83024</v>
+        <v>5177</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>780081</v>
+        <v>780080</v>
       </c>
       <c r="R9" t="n">
-        <v>7274609</v>
+        <v>7274590</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130187798</v>
+        <v>130187862</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>83024</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>779985</v>
+        <v>780081</v>
       </c>
       <c r="R10" t="n">
-        <v>7274468</v>
+        <v>7274609</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1683,32 +1683,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130187844</v>
+        <v>130187825</v>
       </c>
       <c r="B11" t="n">
-        <v>80285</v>
+        <v>80314</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>780089</v>
+        <v>779986</v>
       </c>
       <c r="R11" t="n">
-        <v>7274562</v>
+        <v>7274565</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1907,32 +1907,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130187809</v>
+        <v>130187844</v>
       </c>
       <c r="B13" t="n">
-        <v>5197</v>
+        <v>80285</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>779880</v>
+        <v>780089</v>
       </c>
       <c r="R13" t="n">
-        <v>7274528</v>
+        <v>7274562</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130187825</v>
+        <v>130187809</v>
       </c>
       <c r="B14" t="n">
-        <v>80314</v>
+        <v>5197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,21 +2030,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>779986</v>
+        <v>779880</v>
       </c>
       <c r="R14" t="n">
-        <v>7274565</v>
+        <v>7274528</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2131,32 +2131,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130187814</v>
+        <v>130187819</v>
       </c>
       <c r="B15" t="n">
-        <v>5177</v>
+        <v>83024</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>779905</v>
+        <v>779988</v>
       </c>
       <c r="R15" t="n">
-        <v>7274531</v>
+        <v>7274540</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2243,32 +2243,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130187819</v>
+        <v>130187814</v>
       </c>
       <c r="B16" t="n">
-        <v>83024</v>
+        <v>5177</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>779988</v>
+        <v>779905</v>
       </c>
       <c r="R16" t="n">
-        <v>7274540</v>
+        <v>7274531</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2467,32 +2467,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130187824</v>
+        <v>130187822</v>
       </c>
       <c r="B18" t="n">
-        <v>80189</v>
+        <v>79180</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>779977</v>
+        <v>779971</v>
       </c>
       <c r="R18" t="n">
-        <v>7274568</v>
+        <v>7274563</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2579,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130187872</v>
+        <v>130187824</v>
       </c>
       <c r="B19" t="n">
-        <v>80314</v>
+        <v>80189</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2590,21 +2590,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>780058</v>
+        <v>779977</v>
       </c>
       <c r="R19" t="n">
-        <v>7274593</v>
+        <v>7274568</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2691,32 +2691,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130187822</v>
+        <v>130187872</v>
       </c>
       <c r="B20" t="n">
-        <v>79180</v>
+        <v>80314</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>779971</v>
+        <v>780058</v>
       </c>
       <c r="R20" t="n">
-        <v>7274563</v>
+        <v>7274593</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3139,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130187799</v>
+        <v>130187866</v>
       </c>
       <c r="B24" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3150,21 +3150,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3174,10 +3174,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>779963</v>
+        <v>780074</v>
       </c>
       <c r="R24" t="n">
-        <v>7274490</v>
+        <v>7274597</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3251,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130187866</v>
+        <v>130187799</v>
       </c>
       <c r="B25" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3262,21 +3262,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>780074</v>
+        <v>779963</v>
       </c>
       <c r="R25" t="n">
-        <v>7274597</v>
+        <v>7274490</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3699,32 +3699,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130187808</v>
+        <v>130187826</v>
       </c>
       <c r="B29" t="n">
-        <v>57930</v>
+        <v>80285</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>779883</v>
+        <v>779984</v>
       </c>
       <c r="R29" t="n">
-        <v>7274530</v>
+        <v>7274561</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3811,32 +3811,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130187826</v>
+        <v>130187808</v>
       </c>
       <c r="B30" t="n">
-        <v>80285</v>
+        <v>57930</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>779984</v>
+        <v>779883</v>
       </c>
       <c r="R30" t="n">
-        <v>7274561</v>
+        <v>7274530</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">

--- a/artfynd/A 59832-2023 artfynd.xlsx
+++ b/artfynd/A 59832-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130187874</v>
       </c>
       <c r="B2" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130187821</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130187876</v>
+        <v>130187851</v>
       </c>
       <c r="B4" t="n">
-        <v>80189</v>
+        <v>79183</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>780063</v>
+        <v>780086</v>
       </c>
       <c r="R4" t="n">
-        <v>7274578</v>
+        <v>7274586</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,32 +1011,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130187851</v>
+        <v>130187876</v>
       </c>
       <c r="B5" t="n">
-        <v>79180</v>
+        <v>80192</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>780086</v>
+        <v>780063</v>
       </c>
       <c r="R5" t="n">
-        <v>7274586</v>
+        <v>7274578</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130187798</v>
+        <v>130187862</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>83027</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>779985</v>
+        <v>780081</v>
       </c>
       <c r="R7" t="n">
-        <v>7274468</v>
+        <v>7274609</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1350,7 +1350,7 @@
         <v>130187836</v>
       </c>
       <c r="B8" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,32 +1459,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130187852</v>
+        <v>130187798</v>
       </c>
       <c r="B9" t="n">
-        <v>5177</v>
+        <v>79183</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>780080</v>
+        <v>779985</v>
       </c>
       <c r="R9" t="n">
-        <v>7274590</v>
+        <v>7274468</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1571,32 +1571,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130187862</v>
+        <v>130187852</v>
       </c>
       <c r="B10" t="n">
-        <v>83024</v>
+        <v>5177</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>780081</v>
+        <v>780080</v>
       </c>
       <c r="R10" t="n">
-        <v>7274609</v>
+        <v>7274590</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130187825</v>
+        <v>130187809</v>
       </c>
       <c r="B11" t="n">
-        <v>80314</v>
+        <v>5197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,21 +1694,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>779986</v>
+        <v>779880</v>
       </c>
       <c r="R11" t="n">
-        <v>7274565</v>
+        <v>7274528</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130187805</v>
+        <v>130187844</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>80288</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,21 +1806,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>779884</v>
+        <v>780089</v>
       </c>
       <c r="R12" t="n">
-        <v>7274509</v>
+        <v>7274562</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1907,32 +1907,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130187844</v>
+        <v>130187825</v>
       </c>
       <c r="B13" t="n">
-        <v>80285</v>
+        <v>80317</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>780089</v>
+        <v>779986</v>
       </c>
       <c r="R13" t="n">
-        <v>7274562</v>
+        <v>7274565</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,27 +2019,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130187809</v>
+        <v>130187805</v>
       </c>
       <c r="B14" t="n">
-        <v>5197</v>
+        <v>57823</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>779880</v>
+        <v>779884</v>
       </c>
       <c r="R14" t="n">
-        <v>7274528</v>
+        <v>7274509</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,7 +2134,7 @@
         <v>130187819</v>
       </c>
       <c r="B15" t="n">
-        <v>83024</v>
+        <v>83027</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>130187865</v>
       </c>
       <c r="B17" t="n">
-        <v>80314</v>
+        <v>80317</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2467,32 +2467,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130187822</v>
+        <v>130187824</v>
       </c>
       <c r="B18" t="n">
-        <v>79180</v>
+        <v>80192</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>779971</v>
+        <v>779977</v>
       </c>
       <c r="R18" t="n">
-        <v>7274563</v>
+        <v>7274568</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2579,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130187824</v>
+        <v>130187872</v>
       </c>
       <c r="B19" t="n">
-        <v>80189</v>
+        <v>80317</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2590,21 +2590,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>779977</v>
+        <v>780058</v>
       </c>
       <c r="R19" t="n">
-        <v>7274568</v>
+        <v>7274593</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2691,32 +2691,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130187872</v>
+        <v>130187822</v>
       </c>
       <c r="B20" t="n">
-        <v>80314</v>
+        <v>79183</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>780058</v>
+        <v>779971</v>
       </c>
       <c r="R20" t="n">
-        <v>7274593</v>
+        <v>7274563</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2806,7 +2806,7 @@
         <v>130187832</v>
       </c>
       <c r="B21" t="n">
-        <v>83024</v>
+        <v>83027</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2915,32 +2915,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130187800</v>
+        <v>130187846</v>
       </c>
       <c r="B22" t="n">
-        <v>79180</v>
+        <v>80317</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>779931</v>
+        <v>780089</v>
       </c>
       <c r="R22" t="n">
-        <v>7274494</v>
+        <v>7274562</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3027,32 +3027,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130187846</v>
+        <v>130187800</v>
       </c>
       <c r="B23" t="n">
-        <v>80314</v>
+        <v>79183</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>780089</v>
+        <v>779931</v>
       </c>
       <c r="R23" t="n">
-        <v>7274562</v>
+        <v>7274494</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3139,10 +3139,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130187866</v>
+        <v>130187799</v>
       </c>
       <c r="B24" t="n">
-        <v>80285</v>
+        <v>79183</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3150,21 +3150,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3174,10 +3174,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>780074</v>
+        <v>779963</v>
       </c>
       <c r="R24" t="n">
-        <v>7274597</v>
+        <v>7274490</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3251,10 +3251,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130187799</v>
+        <v>130187866</v>
       </c>
       <c r="B25" t="n">
-        <v>79180</v>
+        <v>80288</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3262,21 +3262,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>779963</v>
+        <v>780074</v>
       </c>
       <c r="R25" t="n">
-        <v>7274490</v>
+        <v>7274597</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3478,7 +3478,7 @@
         <v>130187795</v>
       </c>
       <c r="B27" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>130187841</v>
       </c>
       <c r="B28" t="n">
-        <v>83024</v>
+        <v>83027</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>130187826</v>
       </c>
       <c r="B29" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 59832-2023 artfynd.xlsx
+++ b/artfynd/A 59832-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130187874</v>
       </c>
       <c r="B2" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130187821</v>
+        <v>130187851</v>
       </c>
       <c r="B3" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>779968</v>
+        <v>780086</v>
       </c>
       <c r="R3" t="n">
-        <v>7274543</v>
+        <v>7274586</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130187851</v>
+        <v>130187821</v>
       </c>
       <c r="B4" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>780086</v>
+        <v>779968</v>
       </c>
       <c r="R4" t="n">
-        <v>7274586</v>
+        <v>7274543</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1014,7 +1014,7 @@
         <v>130187876</v>
       </c>
       <c r="B5" t="n">
-        <v>80192</v>
+        <v>80218</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130187862</v>
+        <v>130187836</v>
       </c>
       <c r="B7" t="n">
-        <v>83027</v>
+        <v>79209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>780081</v>
+        <v>780029</v>
       </c>
       <c r="R7" t="n">
-        <v>7274609</v>
+        <v>7274587</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130187836</v>
+        <v>130187798</v>
       </c>
       <c r="B8" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>780029</v>
+        <v>779985</v>
       </c>
       <c r="R8" t="n">
-        <v>7274587</v>
+        <v>7274468</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1459,32 +1459,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130187798</v>
+        <v>130187852</v>
       </c>
       <c r="B9" t="n">
-        <v>79183</v>
+        <v>5177</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>779985</v>
+        <v>780080</v>
       </c>
       <c r="R9" t="n">
-        <v>7274468</v>
+        <v>7274590</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1571,32 +1571,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130187852</v>
+        <v>130187862</v>
       </c>
       <c r="B10" t="n">
-        <v>5177</v>
+        <v>83053</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>780080</v>
+        <v>780081</v>
       </c>
       <c r="R10" t="n">
-        <v>7274590</v>
+        <v>7274609</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1683,32 +1683,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130187809</v>
+        <v>130187844</v>
       </c>
       <c r="B11" t="n">
-        <v>5197</v>
+        <v>80314</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>779880</v>
+        <v>780089</v>
       </c>
       <c r="R11" t="n">
-        <v>7274528</v>
+        <v>7274562</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130187844</v>
+        <v>130187805</v>
       </c>
       <c r="B12" t="n">
-        <v>80288</v>
+        <v>57849</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,21 +1806,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>780089</v>
+        <v>779884</v>
       </c>
       <c r="R12" t="n">
-        <v>7274562</v>
+        <v>7274509</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130187825</v>
+        <v>130187809</v>
       </c>
       <c r="B13" t="n">
-        <v>80317</v>
+        <v>5197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>779986</v>
+        <v>779880</v>
       </c>
       <c r="R13" t="n">
-        <v>7274565</v>
+        <v>7274528</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2019,32 +2019,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130187805</v>
+        <v>130187825</v>
       </c>
       <c r="B14" t="n">
-        <v>57823</v>
+        <v>80343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>779884</v>
+        <v>779986</v>
       </c>
       <c r="R14" t="n">
-        <v>7274509</v>
+        <v>7274565</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2131,32 +2131,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130187819</v>
+        <v>130187814</v>
       </c>
       <c r="B15" t="n">
-        <v>83027</v>
+        <v>5177</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>779988</v>
+        <v>779905</v>
       </c>
       <c r="R15" t="n">
-        <v>7274540</v>
+        <v>7274531</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2243,32 +2243,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130187814</v>
+        <v>130187819</v>
       </c>
       <c r="B16" t="n">
-        <v>5177</v>
+        <v>83053</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>779905</v>
+        <v>779988</v>
       </c>
       <c r="R16" t="n">
-        <v>7274531</v>
+        <v>7274540</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2358,7 +2358,7 @@
         <v>130187865</v>
       </c>
       <c r="B17" t="n">
-        <v>80317</v>
+        <v>80343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>130187824</v>
       </c>
       <c r="B18" t="n">
-        <v>80192</v>
+        <v>80218</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2579,32 +2579,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130187872</v>
+        <v>130187822</v>
       </c>
       <c r="B19" t="n">
-        <v>80317</v>
+        <v>79209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>780058</v>
+        <v>779971</v>
       </c>
       <c r="R19" t="n">
-        <v>7274593</v>
+        <v>7274563</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2691,32 +2691,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130187822</v>
+        <v>130187872</v>
       </c>
       <c r="B20" t="n">
-        <v>79183</v>
+        <v>80343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>779971</v>
+        <v>780058</v>
       </c>
       <c r="R20" t="n">
-        <v>7274563</v>
+        <v>7274593</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2806,7 +2806,7 @@
         <v>130187832</v>
       </c>
       <c r="B21" t="n">
-        <v>83027</v>
+        <v>83053</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2915,32 +2915,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130187846</v>
+        <v>130187800</v>
       </c>
       <c r="B22" t="n">
-        <v>80317</v>
+        <v>79209</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>780089</v>
+        <v>779931</v>
       </c>
       <c r="R22" t="n">
-        <v>7274562</v>
+        <v>7274494</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3027,32 +3027,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130187800</v>
+        <v>130187846</v>
       </c>
       <c r="B23" t="n">
-        <v>79183</v>
+        <v>80343</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>779931</v>
+        <v>780089</v>
       </c>
       <c r="R23" t="n">
-        <v>7274494</v>
+        <v>7274562</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3142,7 +3142,7 @@
         <v>130187799</v>
       </c>
       <c r="B24" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>130187866</v>
       </c>
       <c r="B25" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>130187795</v>
       </c>
       <c r="B27" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>130187841</v>
       </c>
       <c r="B28" t="n">
-        <v>83027</v>
+        <v>83053</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>130187826</v>
       </c>
       <c r="B29" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>130187808</v>
       </c>
       <c r="B30" t="n">
-        <v>57930</v>
+        <v>57956</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 59832-2023 artfynd.xlsx
+++ b/artfynd/A 59832-2023 artfynd.xlsx
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130187836</v>
+        <v>130187862</v>
       </c>
       <c r="B7" t="n">
-        <v>79209</v>
+        <v>83053</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>780029</v>
+        <v>780081</v>
       </c>
       <c r="R7" t="n">
-        <v>7274587</v>
+        <v>7274609</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1347,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130187798</v>
+        <v>130187836</v>
       </c>
       <c r="B8" t="n">
         <v>79209</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>779985</v>
+        <v>780029</v>
       </c>
       <c r="R8" t="n">
-        <v>7274468</v>
+        <v>7274587</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1459,32 +1459,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130187852</v>
+        <v>130187798</v>
       </c>
       <c r="B9" t="n">
-        <v>5177</v>
+        <v>79209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>780080</v>
+        <v>779985</v>
       </c>
       <c r="R9" t="n">
-        <v>7274590</v>
+        <v>7274468</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1571,32 +1571,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130187862</v>
+        <v>130187852</v>
       </c>
       <c r="B10" t="n">
-        <v>83053</v>
+        <v>5177</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>780081</v>
+        <v>780080</v>
       </c>
       <c r="R10" t="n">
-        <v>7274609</v>
+        <v>7274590</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">

--- a/artfynd/A 59832-2023 artfynd.xlsx
+++ b/artfynd/A 59832-2023 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130187851</v>
+        <v>130187821</v>
       </c>
       <c r="B3" t="n">
         <v>79209</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>780086</v>
+        <v>779968</v>
       </c>
       <c r="R3" t="n">
-        <v>7274586</v>
+        <v>7274543</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130187821</v>
+        <v>130187851</v>
       </c>
       <c r="B4" t="n">
         <v>79209</v>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>779968</v>
+        <v>780086</v>
       </c>
       <c r="R4" t="n">
-        <v>7274543</v>
+        <v>7274586</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1238,7 +1238,7 @@
         <v>130187862</v>
       </c>
       <c r="B7" t="n">
-        <v>83053</v>
+        <v>83054</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130187836</v>
+        <v>130187798</v>
       </c>
       <c r="B8" t="n">
         <v>79209</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>780029</v>
+        <v>779985</v>
       </c>
       <c r="R8" t="n">
-        <v>7274587</v>
+        <v>7274468</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1459,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130187798</v>
+        <v>130187836</v>
       </c>
       <c r="B9" t="n">
         <v>79209</v>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>779985</v>
+        <v>780029</v>
       </c>
       <c r="R9" t="n">
-        <v>7274468</v>
+        <v>7274587</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1683,32 +1683,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130187844</v>
+        <v>130187825</v>
       </c>
       <c r="B11" t="n">
-        <v>80314</v>
+        <v>80343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>780089</v>
+        <v>779986</v>
       </c>
       <c r="R11" t="n">
-        <v>7274562</v>
+        <v>7274565</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130187805</v>
+        <v>130187844</v>
       </c>
       <c r="B12" t="n">
-        <v>57849</v>
+        <v>80314</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,21 +1806,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>779884</v>
+        <v>780089</v>
       </c>
       <c r="R12" t="n">
-        <v>7274509</v>
+        <v>7274562</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2019,32 +2019,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130187825</v>
+        <v>130187805</v>
       </c>
       <c r="B14" t="n">
-        <v>80343</v>
+        <v>57849</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>779986</v>
+        <v>779884</v>
       </c>
       <c r="R14" t="n">
-        <v>7274565</v>
+        <v>7274509</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2131,32 +2131,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130187814</v>
+        <v>130187819</v>
       </c>
       <c r="B15" t="n">
-        <v>5177</v>
+        <v>83054</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>779905</v>
+        <v>779988</v>
       </c>
       <c r="R15" t="n">
-        <v>7274531</v>
+        <v>7274540</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2243,32 +2243,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130187819</v>
+        <v>130187814</v>
       </c>
       <c r="B16" t="n">
-        <v>83053</v>
+        <v>5177</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>779988</v>
+        <v>779905</v>
       </c>
       <c r="R16" t="n">
-        <v>7274540</v>
+        <v>7274531</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130187824</v>
+        <v>130187872</v>
       </c>
       <c r="B18" t="n">
-        <v>80218</v>
+        <v>80343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,21 +2478,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>779977</v>
+        <v>780058</v>
       </c>
       <c r="R18" t="n">
-        <v>7274568</v>
+        <v>7274593</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2579,32 +2579,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130187822</v>
+        <v>130187824</v>
       </c>
       <c r="B19" t="n">
-        <v>79209</v>
+        <v>80218</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>779971</v>
+        <v>779977</v>
       </c>
       <c r="R19" t="n">
-        <v>7274563</v>
+        <v>7274568</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2691,32 +2691,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130187872</v>
+        <v>130187822</v>
       </c>
       <c r="B20" t="n">
-        <v>80343</v>
+        <v>79209</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>780058</v>
+        <v>779971</v>
       </c>
       <c r="R20" t="n">
-        <v>7274593</v>
+        <v>7274563</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2806,7 +2806,7 @@
         <v>130187832</v>
       </c>
       <c r="B21" t="n">
-        <v>83053</v>
+        <v>83054</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>130187841</v>
       </c>
       <c r="B28" t="n">
-        <v>83053</v>
+        <v>83054</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3699,32 +3699,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130187826</v>
+        <v>130187808</v>
       </c>
       <c r="B29" t="n">
-        <v>80314</v>
+        <v>57956</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>779984</v>
+        <v>779883</v>
       </c>
       <c r="R29" t="n">
-        <v>7274561</v>
+        <v>7274530</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3811,32 +3811,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130187808</v>
+        <v>130187826</v>
       </c>
       <c r="B30" t="n">
-        <v>57956</v>
+        <v>80314</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>779883</v>
+        <v>779984</v>
       </c>
       <c r="R30" t="n">
-        <v>7274530</v>
+        <v>7274561</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">

--- a/artfynd/A 59832-2023 artfynd.xlsx
+++ b/artfynd/A 59832-2023 artfynd.xlsx
@@ -1235,32 +1235,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130187862</v>
+        <v>130187852</v>
       </c>
       <c r="B7" t="n">
-        <v>83054</v>
+        <v>5177</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>780081</v>
+        <v>780080</v>
       </c>
       <c r="R7" t="n">
-        <v>7274609</v>
+        <v>7274590</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1347,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130187798</v>
+        <v>130187836</v>
       </c>
       <c r="B8" t="n">
         <v>79209</v>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>779985</v>
+        <v>780029</v>
       </c>
       <c r="R8" t="n">
-        <v>7274468</v>
+        <v>7274587</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1459,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130187836</v>
+        <v>130187798</v>
       </c>
       <c r="B9" t="n">
         <v>79209</v>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>780029</v>
+        <v>779985</v>
       </c>
       <c r="R9" t="n">
-        <v>7274587</v>
+        <v>7274468</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1571,32 +1571,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130187852</v>
+        <v>130187862</v>
       </c>
       <c r="B10" t="n">
-        <v>5177</v>
+        <v>83055</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>780080</v>
+        <v>780081</v>
       </c>
       <c r="R10" t="n">
-        <v>7274590</v>
+        <v>7274609</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1907,27 +1907,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130187809</v>
+        <v>130187805</v>
       </c>
       <c r="B13" t="n">
-        <v>5197</v>
+        <v>57849</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>779880</v>
+        <v>779884</v>
       </c>
       <c r="R13" t="n">
-        <v>7274528</v>
+        <v>7274509</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,27 +2019,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130187805</v>
+        <v>130187809</v>
       </c>
       <c r="B14" t="n">
-        <v>57849</v>
+        <v>5197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>779884</v>
+        <v>779880</v>
       </c>
       <c r="R14" t="n">
-        <v>7274509</v>
+        <v>7274528</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,7 +2134,7 @@
         <v>130187819</v>
       </c>
       <c r="B15" t="n">
-        <v>83054</v>
+        <v>83055</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2467,32 +2467,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130187872</v>
+        <v>130187822</v>
       </c>
       <c r="B18" t="n">
-        <v>80343</v>
+        <v>79209</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>780058</v>
+        <v>779971</v>
       </c>
       <c r="R18" t="n">
-        <v>7274593</v>
+        <v>7274563</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2691,32 +2691,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130187822</v>
+        <v>130187872</v>
       </c>
       <c r="B20" t="n">
-        <v>79209</v>
+        <v>80343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>779971</v>
+        <v>780058</v>
       </c>
       <c r="R20" t="n">
-        <v>7274563</v>
+        <v>7274593</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2806,7 +2806,7 @@
         <v>130187832</v>
       </c>
       <c r="B21" t="n">
-        <v>83054</v>
+        <v>83055</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>130187841</v>
       </c>
       <c r="B28" t="n">
-        <v>83054</v>
+        <v>83055</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3699,32 +3699,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130187808</v>
+        <v>130187826</v>
       </c>
       <c r="B29" t="n">
-        <v>57956</v>
+        <v>80314</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>779883</v>
+        <v>779984</v>
       </c>
       <c r="R29" t="n">
-        <v>7274530</v>
+        <v>7274561</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3811,32 +3811,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130187826</v>
+        <v>130187808</v>
       </c>
       <c r="B30" t="n">
-        <v>80314</v>
+        <v>57956</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>779984</v>
+        <v>779883</v>
       </c>
       <c r="R30" t="n">
-        <v>7274561</v>
+        <v>7274530</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">

--- a/artfynd/A 59832-2023 artfynd.xlsx
+++ b/artfynd/A 59832-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130187874</v>
       </c>
       <c r="B2" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130187821</v>
       </c>
       <c r="B3" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130187851</v>
+        <v>130187876</v>
       </c>
       <c r="B4" t="n">
-        <v>79209</v>
+        <v>80220</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>780086</v>
+        <v>780063</v>
       </c>
       <c r="R4" t="n">
-        <v>7274586</v>
+        <v>7274578</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,32 +1011,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130187876</v>
+        <v>130187851</v>
       </c>
       <c r="B5" t="n">
-        <v>80218</v>
+        <v>79211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>780063</v>
+        <v>780086</v>
       </c>
       <c r="R5" t="n">
-        <v>7274578</v>
+        <v>7274586</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1235,32 +1235,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130187852</v>
+        <v>130187836</v>
       </c>
       <c r="B7" t="n">
-        <v>5177</v>
+        <v>79211</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>780080</v>
+        <v>780029</v>
       </c>
       <c r="R7" t="n">
-        <v>7274590</v>
+        <v>7274587</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130187836</v>
+        <v>130187798</v>
       </c>
       <c r="B8" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>780029</v>
+        <v>779985</v>
       </c>
       <c r="R8" t="n">
-        <v>7274587</v>
+        <v>7274468</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130187798</v>
+        <v>130187862</v>
       </c>
       <c r="B9" t="n">
-        <v>79209</v>
+        <v>83057</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,21 +1470,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>779985</v>
+        <v>780081</v>
       </c>
       <c r="R9" t="n">
-        <v>7274468</v>
+        <v>7274609</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1571,32 +1571,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130187862</v>
+        <v>130187852</v>
       </c>
       <c r="B10" t="n">
-        <v>83055</v>
+        <v>5177</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>780081</v>
+        <v>780080</v>
       </c>
       <c r="R10" t="n">
-        <v>7274609</v>
+        <v>7274590</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1683,32 +1683,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130187825</v>
+        <v>130187805</v>
       </c>
       <c r="B11" t="n">
-        <v>80343</v>
+        <v>57851</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>779986</v>
+        <v>779884</v>
       </c>
       <c r="R11" t="n">
-        <v>7274565</v>
+        <v>7274509</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1798,7 +1798,7 @@
         <v>130187844</v>
       </c>
       <c r="B12" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1907,32 +1907,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130187805</v>
+        <v>130187825</v>
       </c>
       <c r="B13" t="n">
-        <v>57849</v>
+        <v>80345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>779884</v>
+        <v>779986</v>
       </c>
       <c r="R13" t="n">
-        <v>7274509</v>
+        <v>7274565</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2134,7 +2134,7 @@
         <v>130187819</v>
       </c>
       <c r="B15" t="n">
-        <v>83055</v>
+        <v>83057</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2358,7 +2358,7 @@
         <v>130187865</v>
       </c>
       <c r="B17" t="n">
-        <v>80343</v>
+        <v>80345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2467,32 +2467,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130187822</v>
+        <v>130187872</v>
       </c>
       <c r="B18" t="n">
-        <v>79209</v>
+        <v>80345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>779971</v>
+        <v>780058</v>
       </c>
       <c r="R18" t="n">
-        <v>7274563</v>
+        <v>7274593</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2579,32 +2579,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130187824</v>
+        <v>130187822</v>
       </c>
       <c r="B19" t="n">
-        <v>80218</v>
+        <v>79211</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>779977</v>
+        <v>779971</v>
       </c>
       <c r="R19" t="n">
-        <v>7274568</v>
+        <v>7274563</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130187872</v>
+        <v>130187824</v>
       </c>
       <c r="B20" t="n">
-        <v>80343</v>
+        <v>80220</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2702,21 +2702,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>780058</v>
+        <v>779977</v>
       </c>
       <c r="R20" t="n">
-        <v>7274593</v>
+        <v>7274568</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2806,7 +2806,7 @@
         <v>130187832</v>
       </c>
       <c r="B21" t="n">
-        <v>83055</v>
+        <v>83057</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
         <v>130187800</v>
       </c>
       <c r="B22" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>130187846</v>
       </c>
       <c r="B23" t="n">
-        <v>80343</v>
+        <v>80345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
         <v>130187799</v>
       </c>
       <c r="B24" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>130187866</v>
       </c>
       <c r="B25" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>130187795</v>
       </c>
       <c r="B27" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>130187841</v>
       </c>
       <c r="B28" t="n">
-        <v>83055</v>
+        <v>83057</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>130187826</v>
       </c>
       <c r="B29" t="n">
-        <v>80314</v>
+        <v>80316</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3814,7 +3814,7 @@
         <v>130187808</v>
       </c>
       <c r="B30" t="n">
-        <v>57956</v>
+        <v>57958</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 59832-2023 artfynd.xlsx
+++ b/artfynd/A 59832-2023 artfynd.xlsx
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130187821</v>
+        <v>130187876</v>
       </c>
       <c r="B3" t="n">
-        <v>79211</v>
+        <v>80220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>779968</v>
+        <v>780063</v>
       </c>
       <c r="R3" t="n">
-        <v>7274543</v>
+        <v>7274578</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -899,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130187876</v>
+        <v>130187851</v>
       </c>
       <c r="B4" t="n">
-        <v>80220</v>
+        <v>79211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>780063</v>
+        <v>780086</v>
       </c>
       <c r="R4" t="n">
-        <v>7274578</v>
+        <v>7274586</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130187851</v>
+        <v>130187821</v>
       </c>
       <c r="B5" t="n">
         <v>79211</v>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>780086</v>
+        <v>779968</v>
       </c>
       <c r="R5" t="n">
-        <v>7274586</v>
+        <v>7274543</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1459,32 +1459,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130187862</v>
+        <v>130187852</v>
       </c>
       <c r="B9" t="n">
-        <v>83057</v>
+        <v>5177</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>780081</v>
+        <v>780080</v>
       </c>
       <c r="R9" t="n">
-        <v>7274609</v>
+        <v>7274590</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1571,32 +1571,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130187852</v>
+        <v>130187862</v>
       </c>
       <c r="B10" t="n">
-        <v>5177</v>
+        <v>83057</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>780080</v>
+        <v>780081</v>
       </c>
       <c r="R10" t="n">
-        <v>7274590</v>
+        <v>7274609</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1683,27 +1683,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130187805</v>
+        <v>130187809</v>
       </c>
       <c r="B11" t="n">
-        <v>57851</v>
+        <v>5197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>779884</v>
+        <v>779880</v>
       </c>
       <c r="R11" t="n">
-        <v>7274509</v>
+        <v>7274528</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,32 +1795,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130187844</v>
+        <v>130187825</v>
       </c>
       <c r="B12" t="n">
-        <v>80316</v>
+        <v>80345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>780089</v>
+        <v>779986</v>
       </c>
       <c r="R12" t="n">
-        <v>7274562</v>
+        <v>7274565</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,32 +1907,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130187825</v>
+        <v>130187844</v>
       </c>
       <c r="B13" t="n">
-        <v>80345</v>
+        <v>80316</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>779986</v>
+        <v>780089</v>
       </c>
       <c r="R13" t="n">
-        <v>7274565</v>
+        <v>7274562</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,27 +2019,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130187809</v>
+        <v>130187805</v>
       </c>
       <c r="B14" t="n">
-        <v>5197</v>
+        <v>57851</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>779880</v>
+        <v>779884</v>
       </c>
       <c r="R14" t="n">
-        <v>7274528</v>
+        <v>7274509</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2467,32 +2467,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130187872</v>
+        <v>130187822</v>
       </c>
       <c r="B18" t="n">
-        <v>80345</v>
+        <v>79211</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>780058</v>
+        <v>779971</v>
       </c>
       <c r="R18" t="n">
-        <v>7274593</v>
+        <v>7274563</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2579,32 +2579,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130187822</v>
+        <v>130187824</v>
       </c>
       <c r="B19" t="n">
-        <v>79211</v>
+        <v>80220</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>779971</v>
+        <v>779977</v>
       </c>
       <c r="R19" t="n">
-        <v>7274563</v>
+        <v>7274568</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130187824</v>
+        <v>130187872</v>
       </c>
       <c r="B20" t="n">
-        <v>80220</v>
+        <v>80345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2702,21 +2702,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>779977</v>
+        <v>780058</v>
       </c>
       <c r="R20" t="n">
-        <v>7274568</v>
+        <v>7274593</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2915,32 +2915,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130187800</v>
+        <v>130187846</v>
       </c>
       <c r="B22" t="n">
-        <v>79211</v>
+        <v>80345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>779931</v>
+        <v>780089</v>
       </c>
       <c r="R22" t="n">
-        <v>7274494</v>
+        <v>7274562</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3027,32 +3027,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130187846</v>
+        <v>130187800</v>
       </c>
       <c r="B23" t="n">
-        <v>80345</v>
+        <v>79211</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>780089</v>
+        <v>779931</v>
       </c>
       <c r="R23" t="n">
-        <v>7274562</v>
+        <v>7274494</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3699,32 +3699,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130187826</v>
+        <v>130187808</v>
       </c>
       <c r="B29" t="n">
-        <v>80316</v>
+        <v>57958</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>779984</v>
+        <v>779883</v>
       </c>
       <c r="R29" t="n">
-        <v>7274561</v>
+        <v>7274530</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3779,7 +3779,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3811,32 +3811,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130187808</v>
+        <v>130187826</v>
       </c>
       <c r="B30" t="n">
-        <v>57958</v>
+        <v>80316</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>779883</v>
+        <v>779984</v>
       </c>
       <c r="R30" t="n">
-        <v>7274530</v>
+        <v>7274561</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">

--- a/artfynd/A 59832-2023 artfynd.xlsx
+++ b/artfynd/A 59832-2023 artfynd.xlsx
@@ -3702,7 +3702,7 @@
         <v>130187808</v>
       </c>
       <c r="B29" t="n">
-        <v>57958</v>
+        <v>57968</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 59832-2023 artfynd.xlsx
+++ b/artfynd/A 59832-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130187874</v>
+        <v>130187819</v>
       </c>
       <c r="B2" t="n">
-        <v>80316</v>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>780057</v>
+        <v>779988</v>
       </c>
       <c r="R2" t="n">
-        <v>7274592</v>
+        <v>7274540</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130187876</v>
+        <v>130187832</v>
       </c>
       <c r="B3" t="n">
-        <v>80220</v>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>780063</v>
+        <v>779985</v>
       </c>
       <c r="R3" t="n">
-        <v>7274578</v>
+        <v>7274554</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130187851</v>
+        <v>130187841</v>
       </c>
       <c r="B4" t="n">
-        <v>79211</v>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>780086</v>
+        <v>780091</v>
       </c>
       <c r="R4" t="n">
-        <v>7274586</v>
+        <v>7274556</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130187821</v>
+        <v>130187862</v>
       </c>
       <c r="B5" t="n">
-        <v>79211</v>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>779968</v>
+        <v>780081</v>
       </c>
       <c r="R5" t="n">
-        <v>7274543</v>
+        <v>7274609</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,32 +1123,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130187794</v>
+        <v>130187795</v>
       </c>
       <c r="B6" t="n">
-        <v>5197</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>779929</v>
+        <v>779950</v>
       </c>
       <c r="R6" t="n">
-        <v>7274460</v>
+        <v>7274454</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,14 +1235,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130187836</v>
+        <v>130187798</v>
       </c>
       <c r="B7" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>780029</v>
+        <v>779985</v>
       </c>
       <c r="R7" t="n">
-        <v>7274587</v>
+        <v>7274468</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1347,14 +1347,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130187798</v>
+        <v>130187799</v>
       </c>
       <c r="B8" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>779985</v>
+        <v>779963</v>
       </c>
       <c r="R8" t="n">
-        <v>7274468</v>
+        <v>7274490</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,32 +1459,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130187852</v>
+        <v>130187800</v>
       </c>
       <c r="B9" t="n">
-        <v>5177</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>780080</v>
+        <v>779931</v>
       </c>
       <c r="R9" t="n">
-        <v>7274590</v>
+        <v>7274494</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1571,32 +1571,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130187862</v>
+        <v>130187821</v>
       </c>
       <c r="B10" t="n">
-        <v>83057</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>780081</v>
+        <v>779968</v>
       </c>
       <c r="R10" t="n">
-        <v>7274609</v>
+        <v>7274543</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,32 +1683,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130187809</v>
+        <v>130187822</v>
       </c>
       <c r="B11" t="n">
-        <v>5197</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>779880</v>
+        <v>779971</v>
       </c>
       <c r="R11" t="n">
-        <v>7274528</v>
+        <v>7274563</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1795,32 +1795,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130187825</v>
+        <v>130187836</v>
       </c>
       <c r="B12" t="n">
-        <v>80345</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>779986</v>
+        <v>780029</v>
       </c>
       <c r="R12" t="n">
-        <v>7274565</v>
+        <v>7274587</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1907,32 +1907,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130187844</v>
+        <v>130187851</v>
       </c>
       <c r="B13" t="n">
-        <v>80316</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>780089</v>
+        <v>780086</v>
       </c>
       <c r="R13" t="n">
-        <v>7274562</v>
+        <v>7274586</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2019,32 +2019,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130187805</v>
+        <v>130187824</v>
       </c>
       <c r="B14" t="n">
-        <v>57851</v>
+        <v>80336</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>779884</v>
+        <v>779977</v>
       </c>
       <c r="R14" t="n">
-        <v>7274509</v>
+        <v>7274568</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2131,32 +2131,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130187819</v>
+        <v>130187876</v>
       </c>
       <c r="B15" t="n">
-        <v>83057</v>
+        <v>80336</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>779988</v>
+        <v>780063</v>
       </c>
       <c r="R15" t="n">
-        <v>7274540</v>
+        <v>7274578</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2243,32 +2243,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130187814</v>
+        <v>130187826</v>
       </c>
       <c r="B16" t="n">
-        <v>5177</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>779905</v>
+        <v>779984</v>
       </c>
       <c r="R16" t="n">
-        <v>7274531</v>
+        <v>7274561</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2355,32 +2355,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130187865</v>
+        <v>130187844</v>
       </c>
       <c r="B17" t="n">
-        <v>80345</v>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2390,10 +2390,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>780074</v>
+        <v>780089</v>
       </c>
       <c r="R17" t="n">
-        <v>7274597</v>
+        <v>7274562</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2467,10 +2467,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130187822</v>
+        <v>130187866</v>
       </c>
       <c r="B18" t="n">
-        <v>79211</v>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,21 +2478,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2502,10 +2502,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>779971</v>
+        <v>780074</v>
       </c>
       <c r="R18" t="n">
-        <v>7274563</v>
+        <v>7274597</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2579,32 +2579,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130187824</v>
+        <v>130187874</v>
       </c>
       <c r="B19" t="n">
-        <v>80220</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>779977</v>
+        <v>780057</v>
       </c>
       <c r="R19" t="n">
-        <v>7274568</v>
+        <v>7274592</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2691,10 +2691,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130187872</v>
+        <v>130187825</v>
       </c>
       <c r="B20" t="n">
-        <v>80345</v>
+        <v>80461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2726,10 +2726,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>780058</v>
+        <v>779986</v>
       </c>
       <c r="R20" t="n">
-        <v>7274593</v>
+        <v>7274565</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2803,32 +2803,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130187832</v>
+        <v>130187846</v>
       </c>
       <c r="B21" t="n">
-        <v>83057</v>
+        <v>80461</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>779985</v>
+        <v>780089</v>
       </c>
       <c r="R21" t="n">
-        <v>7274554</v>
+        <v>7274562</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2915,10 +2915,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130187846</v>
+        <v>130187861</v>
       </c>
       <c r="B22" t="n">
-        <v>80345</v>
+        <v>80461</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2950,10 +2950,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>780089</v>
+        <v>780094</v>
       </c>
       <c r="R22" t="n">
-        <v>7274562</v>
+        <v>7274615</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3027,32 +3027,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130187800</v>
+        <v>130187865</v>
       </c>
       <c r="B23" t="n">
-        <v>79211</v>
+        <v>80461</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>779931</v>
+        <v>780074</v>
       </c>
       <c r="R23" t="n">
-        <v>7274494</v>
+        <v>7274597</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3139,32 +3139,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130187799</v>
+        <v>130187872</v>
       </c>
       <c r="B24" t="n">
-        <v>79211</v>
+        <v>80461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3174,10 +3174,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>779963</v>
+        <v>780058</v>
       </c>
       <c r="R24" t="n">
-        <v>7274490</v>
+        <v>7274593</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3251,32 +3251,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130187866</v>
+        <v>130187805</v>
       </c>
       <c r="B25" t="n">
-        <v>80316</v>
+        <v>57950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>780074</v>
+        <v>779884</v>
       </c>
       <c r="R25" t="n">
-        <v>7274597</v>
+        <v>7274509</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3363,10 +3363,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130187823</v>
+        <v>130187814</v>
       </c>
       <c r="B26" t="n">
-        <v>8440</v>
+        <v>5179</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3374,21 +3374,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3398,10 +3398,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>779971</v>
+        <v>779905</v>
       </c>
       <c r="R26" t="n">
-        <v>7274570</v>
+        <v>7274531</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3475,32 +3475,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130187795</v>
+        <v>130187852</v>
       </c>
       <c r="B27" t="n">
-        <v>79211</v>
+        <v>5179</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3510,10 +3510,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>779950</v>
+        <v>780080</v>
       </c>
       <c r="R27" t="n">
-        <v>7274454</v>
+        <v>7274590</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3555,7 +3555,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3587,32 +3587,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130187841</v>
+        <v>130187860</v>
       </c>
       <c r="B28" t="n">
-        <v>83057</v>
+        <v>5173</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>102185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Aromia moschata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>780091</v>
+        <v>780095</v>
       </c>
       <c r="R28" t="n">
-        <v>7274556</v>
+        <v>7274618</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3702,11 +3702,11 @@
         <v>130187808</v>
       </c>
       <c r="B29" t="n">
-        <v>57988</v>
+        <v>58057</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3811,32 +3811,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130187826</v>
+        <v>130187794</v>
       </c>
       <c r="B30" t="n">
-        <v>80316</v>
+        <v>5199</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>105930</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3846,10 +3846,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>779984</v>
+        <v>779929</v>
       </c>
       <c r="R30" t="n">
-        <v>7274561</v>
+        <v>7274460</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3920,6 +3920,230 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130187809</v>
+      </c>
+      <c r="B31" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Boden-Skellefteå, Nb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>779880</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7274528</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>NVI (C250260) Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130187823</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Boden-Skellefteå, Nb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>779971</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7274570</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-05</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>NVI (C250260) Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59832-2023 artfynd.xlsx
+++ b/artfynd/A 59832-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187819</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187832</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187841</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187862</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187795</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187798</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1456,6 +1491,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187799</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1568,6 +1608,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187800</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1680,6 +1725,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187821</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1792,6 +1842,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187822</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1904,6 +1959,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187836</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2016,6 +2076,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187851</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2128,6 +2193,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187824</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2240,6 +2310,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187876</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2352,6 +2427,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187826</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2464,6 +2544,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187844</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2576,6 +2661,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187866</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2688,6 +2778,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187874</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2800,6 +2895,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187825</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2912,6 +3012,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187846</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3024,6 +3129,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187861</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3136,6 +3246,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187865</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3248,6 +3363,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187872</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3360,6 +3480,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187805</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3472,6 +3597,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187814</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3584,6 +3714,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187852</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3696,6 +3831,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187860</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3808,6 +3948,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187808</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3920,6 +4065,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187794</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4032,6 +4182,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187809</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4144,8 +4299,46 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130187823</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>